--- a/results/logs/model_params.xlsx
+++ b/results/logs/model_params.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>window</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>season_length</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,7 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,6 +491,7 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +510,7 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -521,6 +529,7 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -539,6 +548,7 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,6 +567,7 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -575,6 +586,7 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -593,6 +605,7 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -611,6 +624,7 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -629,6 +643,7 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -647,6 +662,7 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -665,6 +681,7 @@
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -683,6 +700,7 @@
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -701,6 +719,7 @@
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -719,6 +738,7 @@
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -737,6 +757,7 @@
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -755,6 +776,7 @@
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -773,6 +795,7 @@
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -791,6 +814,7 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -809,6 +833,7 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -827,6 +852,7 @@
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -845,6 +871,7 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -863,6 +890,7 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -881,6 +909,7 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -899,6 +928,7 @@
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -917,6 +947,7 @@
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -935,6 +966,4165 @@
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/logs/model_params.xlsx
+++ b/results/logs/model_params.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:G250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,16 @@
           <t>season_length</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -473,6 +483,8 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,6 +504,8 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,6 +525,8 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -530,6 +546,8 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,6 +567,8 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -568,6 +588,8 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -587,6 +609,8 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -606,6 +630,8 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -625,6 +651,8 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -644,6 +672,8 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -663,6 +693,8 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -682,6 +714,8 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -701,6 +735,8 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -720,6 +756,8 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -739,6 +777,8 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -758,6 +798,8 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -777,6 +819,8 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -796,6 +840,8 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -815,6 +861,8 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -834,6 +882,8 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -853,6 +903,8 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -872,6 +924,8 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -891,6 +945,8 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -910,6 +966,8 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -929,6 +987,8 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -948,6 +1008,8 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -967,6 +1029,8 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -988,6 +1052,8 @@
       <c r="E29" t="n">
         <v>1</v>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1009,6 +1075,8 @@
       <c r="E30" t="n">
         <v>1</v>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1030,6 +1098,8 @@
       <c r="E31" t="n">
         <v>1</v>
       </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1051,6 +1121,8 @@
       <c r="E32" t="n">
         <v>1</v>
       </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1072,6 +1144,8 @@
       <c r="E33" t="n">
         <v>1</v>
       </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1093,6 +1167,8 @@
       <c r="E34" t="n">
         <v>1</v>
       </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1114,6 +1190,8 @@
       <c r="E35" t="n">
         <v>1</v>
       </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1135,6 +1213,8 @@
       <c r="E36" t="n">
         <v>1</v>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1156,6 +1236,8 @@
       <c r="E37" t="n">
         <v>1</v>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1177,6 +1259,8 @@
       <c r="E38" t="n">
         <v>1</v>
       </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1198,6 +1282,8 @@
       <c r="E39" t="n">
         <v>1</v>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1219,6 +1305,8 @@
       <c r="E40" t="n">
         <v>1</v>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1240,6 +1328,8 @@
       <c r="E41" t="n">
         <v>1</v>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1261,6 +1351,8 @@
       <c r="E42" t="n">
         <v>1</v>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1282,6 +1374,8 @@
       <c r="E43" t="n">
         <v>1</v>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1303,6 +1397,8 @@
       <c r="E44" t="n">
         <v>1</v>
       </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1324,6 +1420,8 @@
       <c r="E45" t="n">
         <v>1</v>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1345,6 +1443,8 @@
       <c r="E46" t="n">
         <v>1</v>
       </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1366,6 +1466,8 @@
       <c r="E47" t="n">
         <v>1</v>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1387,6 +1489,8 @@
       <c r="E48" t="n">
         <v>1</v>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1408,6 +1512,8 @@
       <c r="E49" t="n">
         <v>1</v>
       </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1429,6 +1535,8 @@
       <c r="E50" t="n">
         <v>1</v>
       </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1450,6 +1558,8 @@
       <c r="E51" t="n">
         <v>1</v>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1471,6 +1581,8 @@
       <c r="E52" t="n">
         <v>1</v>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1492,6 +1604,8 @@
       <c r="E53" t="n">
         <v>1</v>
       </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1513,6 +1627,8 @@
       <c r="E54" t="n">
         <v>1</v>
       </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1534,6 +1650,8 @@
       <c r="E55" t="n">
         <v>1</v>
       </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1553,6 +1671,8 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1572,6 +1692,8 @@
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1591,6 +1713,8 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1610,6 +1734,8 @@
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1629,6 +1755,8 @@
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1648,6 +1776,8 @@
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1667,6 +1797,8 @@
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1686,6 +1818,8 @@
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1705,6 +1839,8 @@
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1724,6 +1860,8 @@
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1743,6 +1881,8 @@
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1762,6 +1902,8 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1781,6 +1923,8 @@
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1800,6 +1944,8 @@
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1819,6 +1965,8 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1838,6 +1986,8 @@
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1857,6 +2007,8 @@
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1876,6 +2028,8 @@
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1895,6 +2049,8 @@
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1914,6 +2070,8 @@
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1933,6 +2091,8 @@
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1952,6 +2112,8 @@
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1971,6 +2133,8 @@
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1990,6 +2154,8 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2009,6 +2175,8 @@
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2028,6 +2196,8 @@
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2047,6 +2217,8 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2066,6 +2238,8 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2085,6 +2259,8 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2104,6 +2280,8 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2123,6 +2301,8 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2142,6 +2322,8 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2161,6 +2343,8 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2180,6 +2364,8 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2199,6 +2385,8 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2218,6 +2406,8 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2237,6 +2427,8 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2256,6 +2448,8 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2275,6 +2469,8 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2294,6 +2490,8 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2313,6 +2511,8 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2332,6 +2532,8 @@
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2351,6 +2553,8 @@
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2370,6 +2574,8 @@
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2389,6 +2595,8 @@
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2408,6 +2616,8 @@
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2427,6 +2637,8 @@
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2446,6 +2658,8 @@
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2465,6 +2679,8 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2484,6 +2700,8 @@
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2503,6 +2721,8 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2522,6 +2742,8 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2541,6 +2763,8 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2560,6 +2784,8 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2579,6 +2805,8 @@
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2598,6 +2826,8 @@
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2617,6 +2847,8 @@
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2636,6 +2868,8 @@
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2655,6 +2889,8 @@
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2674,6 +2910,8 @@
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2693,6 +2931,8 @@
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2712,6 +2952,8 @@
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2731,6 +2973,8 @@
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2750,6 +2994,8 @@
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2769,6 +3015,8 @@
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2788,6 +3036,8 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2807,6 +3057,8 @@
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2826,6 +3078,8 @@
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2845,6 +3099,8 @@
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2864,6 +3120,8 @@
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2883,6 +3141,8 @@
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2902,6 +3162,8 @@
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2921,6 +3183,8 @@
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2940,6 +3204,8 @@
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2959,6 +3225,8 @@
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2978,6 +3246,8 @@
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2997,6 +3267,8 @@
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3016,6 +3288,8 @@
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3035,6 +3309,8 @@
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3054,6 +3330,8 @@
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3073,6 +3351,8 @@
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3092,6 +3372,8 @@
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3111,6 +3393,8 @@
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3130,6 +3414,8 @@
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3149,6 +3435,8 @@
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3168,6 +3456,8 @@
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3187,6 +3477,8 @@
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3206,6 +3498,8 @@
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3225,6 +3519,8 @@
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3244,6 +3540,8 @@
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3263,6 +3561,8 @@
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3282,6 +3582,8 @@
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3301,6 +3603,8 @@
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3320,6 +3624,8 @@
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3339,6 +3645,8 @@
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3358,6 +3666,8 @@
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3377,6 +3687,8 @@
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3396,6 +3708,8 @@
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3415,6 +3729,8 @@
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3434,6 +3750,8 @@
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3453,6 +3771,8 @@
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3472,6 +3792,8 @@
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3491,6 +3813,8 @@
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3510,6 +3834,8 @@
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3529,6 +3855,8 @@
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3548,6 +3876,8 @@
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3567,6 +3897,8 @@
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3586,6 +3918,8 @@
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3605,6 +3939,8 @@
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3624,6 +3960,8 @@
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3643,6 +3981,8 @@
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3662,6 +4002,8 @@
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3681,6 +4023,8 @@
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3700,6 +4044,8 @@
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3719,6 +4065,8 @@
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3738,6 +4086,8 @@
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3757,6 +4107,8 @@
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3776,6 +4128,8 @@
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3795,6 +4149,8 @@
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3814,6 +4170,8 @@
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3833,6 +4191,8 @@
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3852,6 +4212,8 @@
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3871,6 +4233,8 @@
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3890,6 +4254,8 @@
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3909,6 +4275,8 @@
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3928,6 +4296,8 @@
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3947,6 +4317,8 @@
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3966,6 +4338,8 @@
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3985,6 +4359,8 @@
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4004,6 +4380,8 @@
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4023,6 +4401,8 @@
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4042,6 +4422,8 @@
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4061,6 +4443,8 @@
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4080,6 +4464,8 @@
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4099,6 +4485,8 @@
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4118,6 +4506,8 @@
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4137,6 +4527,8 @@
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4156,6 +4548,8 @@
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4175,6 +4569,8 @@
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4194,6 +4590,8 @@
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4213,6 +4611,8 @@
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4232,6 +4632,8 @@
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4251,6 +4653,8 @@
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4270,6 +4674,8 @@
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4289,6 +4695,8 @@
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4308,6 +4716,8 @@
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4327,6 +4737,8 @@
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4346,6 +4758,8 @@
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4365,6 +4779,8 @@
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4384,6 +4800,8 @@
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4403,6 +4821,8 @@
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4422,6 +4842,8 @@
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4441,6 +4863,8 @@
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4460,6 +4884,8 @@
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4479,6 +4905,8 @@
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4498,6 +4926,8 @@
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4517,6 +4947,8 @@
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4536,6 +4968,8 @@
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4555,6 +4989,8 @@
       </c>
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4574,6 +5010,8 @@
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4593,6 +5031,8 @@
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4612,6 +5052,8 @@
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4631,6 +5073,8 @@
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4650,6 +5094,8 @@
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4669,6 +5115,8 @@
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4688,6 +5136,8 @@
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4707,6 +5157,8 @@
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4726,6 +5178,8 @@
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4745,6 +5199,8 @@
       </c>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4764,6 +5220,8 @@
       </c>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4783,6 +5241,8 @@
       </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4802,6 +5262,8 @@
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4821,6 +5283,8 @@
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4840,6 +5304,8 @@
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4859,6 +5325,8 @@
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4878,6 +5346,8 @@
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4897,6 +5367,8 @@
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4916,6 +5388,8 @@
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4935,6 +5409,8 @@
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4954,6 +5430,8 @@
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4973,6 +5451,8 @@
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4992,6 +5472,8 @@
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5011,6 +5493,8 @@
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5030,6 +5514,8 @@
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5049,6 +5535,8 @@
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5068,6 +5556,8 @@
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5087,6 +5577,8 @@
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5106,6 +5598,8 @@
       </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5125,6 +5619,158 @@
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="n">
+        <v>2</v>
+      </c>
+      <c r="G246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="n">
+        <v>2</v>
+      </c>
+      <c r="G248" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="n">
+        <v>2</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/logs/model_params.xlsx
+++ b/results/logs/model_params.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G250"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>q</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>d</t>
         </is>
       </c>
     </row>
@@ -485,6 +490,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,6 +512,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -527,6 +534,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -548,6 +556,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,6 +578,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -590,6 +600,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -611,6 +622,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -632,6 +644,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -653,6 +666,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -674,6 +688,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -695,6 +710,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -716,6 +732,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -737,6 +754,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -758,6 +776,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -779,6 +798,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -800,6 +820,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -821,6 +842,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -842,6 +864,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -863,6 +886,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -884,6 +908,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -905,6 +930,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -926,6 +952,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -947,6 +974,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -968,6 +996,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -989,6 +1018,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1010,6 +1040,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1031,6 +1062,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1054,6 +1086,7 @@
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1077,6 +1110,7 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1100,6 +1134,7 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1123,6 +1158,7 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1146,6 +1182,7 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1169,6 +1206,7 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1192,6 +1230,7 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1215,6 +1254,7 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1238,6 +1278,7 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1261,6 +1302,7 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1284,6 +1326,7 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1307,6 +1350,7 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1330,6 +1374,7 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1353,6 +1398,7 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1376,6 +1422,7 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1399,6 +1446,7 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1422,6 +1470,7 @@
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1445,6 +1494,7 @@
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1468,6 +1518,7 @@
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1491,6 +1542,7 @@
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1514,6 +1566,7 @@
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1537,6 +1590,7 @@
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1560,6 +1614,7 @@
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1583,6 +1638,7 @@
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1606,6 +1662,7 @@
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1629,6 +1686,7 @@
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1652,6 +1710,7 @@
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1673,6 +1732,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1694,6 +1754,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1715,6 +1776,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1736,6 +1798,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1757,6 +1820,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1778,6 +1842,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1799,6 +1864,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1820,6 +1886,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1841,6 +1908,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1862,6 +1930,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1883,6 +1952,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1904,6 +1974,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1925,6 +1996,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1946,6 +2018,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1967,6 +2040,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1988,6 +2062,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2009,6 +2084,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2030,6 +2106,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2051,6 +2128,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2072,6 +2150,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2093,6 +2172,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2114,6 +2194,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2135,6 +2216,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2156,6 +2238,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2177,6 +2260,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2198,6 +2282,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2219,6 +2304,7 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2240,6 +2326,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2261,6 +2348,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2282,6 +2370,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2303,6 +2392,7 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2324,6 +2414,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2345,6 +2436,7 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2366,6 +2458,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2387,6 +2480,7 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2408,6 +2502,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2429,6 +2524,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2450,6 +2546,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2471,6 +2568,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2492,6 +2590,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2513,6 +2612,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2534,6 +2634,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2555,6 +2656,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2576,6 +2678,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2597,6 +2700,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2618,6 +2722,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2639,6 +2744,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2660,6 +2766,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2681,6 +2788,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2702,6 +2810,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2723,6 +2832,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2744,6 +2854,7 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2765,6 +2876,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2786,6 +2898,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2807,6 +2920,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2828,6 +2942,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2849,6 +2964,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2870,6 +2986,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2891,6 +3008,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2912,6 +3030,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2933,6 +3052,7 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2954,6 +3074,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2975,6 +3096,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2996,6 +3118,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3017,6 +3140,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3038,6 +3162,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3059,6 +3184,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3080,6 +3206,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3101,6 +3228,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3122,6 +3250,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3143,6 +3272,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3164,6 +3294,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3185,6 +3316,7 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3206,6 +3338,7 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3227,6 +3360,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3248,6 +3382,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3269,6 +3404,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3290,6 +3426,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3311,6 +3448,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3332,6 +3470,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3353,6 +3492,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3374,6 +3514,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3395,6 +3536,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3416,6 +3558,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3437,6 +3580,7 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3458,6 +3602,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3479,6 +3624,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3500,6 +3646,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3521,6 +3668,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3542,6 +3690,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3563,6 +3712,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3584,6 +3734,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3605,6 +3756,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3626,6 +3778,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3647,6 +3800,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3668,6 +3822,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3689,6 +3844,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3710,6 +3866,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3731,6 +3888,7 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3752,6 +3910,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3773,6 +3932,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3794,6 +3954,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3815,6 +3976,7 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3836,6 +3998,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3857,6 +4020,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3878,6 +4042,7 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3899,6 +4064,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3920,6 +4086,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3941,6 +4108,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3962,6 +4130,7 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3983,6 +4152,7 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4004,6 +4174,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4025,6 +4196,7 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4046,6 +4218,7 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4067,6 +4240,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4088,6 +4262,7 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4109,6 +4284,7 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4130,6 +4306,7 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4151,6 +4328,7 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4172,6 +4350,7 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4193,6 +4372,7 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4214,6 +4394,7 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4235,6 +4416,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4256,6 +4438,7 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4277,6 +4460,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4298,6 +4482,7 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4319,6 +4504,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4340,6 +4526,7 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4361,6 +4548,7 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4382,6 +4570,7 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4403,6 +4592,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4424,6 +4614,7 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4445,6 +4636,7 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4466,6 +4658,7 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4487,6 +4680,7 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4508,6 +4702,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4529,6 +4724,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4550,6 +4746,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4571,6 +4768,7 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4592,6 +4790,7 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4613,6 +4812,7 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4634,6 +4834,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4655,6 +4856,7 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4676,6 +4878,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4697,6 +4900,7 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4718,6 +4922,7 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4739,6 +4944,7 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4760,6 +4966,7 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4781,6 +4988,7 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4802,6 +5010,7 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4823,6 +5032,7 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4844,6 +5054,7 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4865,6 +5076,7 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4886,6 +5098,7 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4907,6 +5120,7 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4928,6 +5142,7 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4949,6 +5164,7 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4970,6 +5186,7 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4991,6 +5208,7 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5012,6 +5230,7 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5033,6 +5252,7 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5054,6 +5274,7 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5075,6 +5296,7 @@
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5096,6 +5318,7 @@
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5117,6 +5340,7 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5138,6 +5362,7 @@
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5159,6 +5384,7 @@
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5180,6 +5406,7 @@
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5201,6 +5428,7 @@
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5222,6 +5450,7 @@
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5243,6 +5472,7 @@
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5264,6 +5494,7 @@
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5285,6 +5516,7 @@
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5306,6 +5538,7 @@
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5327,6 +5560,7 @@
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5348,6 +5582,7 @@
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5369,6 +5604,7 @@
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5390,6 +5626,7 @@
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5411,6 +5648,7 @@
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5432,6 +5670,7 @@
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5453,6 +5692,7 @@
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5474,6 +5714,7 @@
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5495,6 +5736,7 @@
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5516,6 +5758,7 @@
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5537,6 +5780,7 @@
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5558,6 +5802,7 @@
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5579,6 +5824,7 @@
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5600,6 +5846,7 @@
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5621,6 +5868,7 @@
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5640,10 +5888,9 @@
       </c>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="n">
-        <v>1</v>
-      </c>
-      <c r="G245" t="n">
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5665,11 +5912,10 @@
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="n">
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="n">
         <v>2</v>
-      </c>
-      <c r="G246" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -5690,10 +5936,9 @@
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
-      <c r="F247" t="n">
-        <v>1</v>
-      </c>
-      <c r="G247" t="n">
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5715,11 +5960,10 @@
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="n">
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="n">
         <v>2</v>
-      </c>
-      <c r="G248" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -5740,10 +5984,9 @@
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
-      <c r="F249" t="n">
-        <v>1</v>
-      </c>
-      <c r="G249" t="n">
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5765,11 +6008,1522 @@
       </c>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr"/>
-      <c r="F250" t="n">
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="n">
         <v>2</v>
       </c>
-      <c r="G250" t="n">
-        <v>1</v>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1</v>
+      </c>
+      <c r="H251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>1</v>
+      </c>
+      <c r="H256" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>1</v>
+      </c>
+      <c r="H259" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>1</v>
+      </c>
+      <c r="H260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>1</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>1</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1</v>
+      </c>
+      <c r="H269" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>1</v>
+      </c>
+      <c r="H270" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1</v>
+      </c>
+      <c r="H271" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>1</v>
+      </c>
+      <c r="H272" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>1</v>
+      </c>
+      <c r="H274" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1</v>
+      </c>
+      <c r="H276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Future MA</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>2</v>
+      </c>
+      <c r="H278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>1</v>
+      </c>
+      <c r="H279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>2</v>
+      </c>
+      <c r="H280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>1</v>
+      </c>
+      <c r="H284" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>2</v>
+      </c>
+      <c r="H285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="n">
+        <v>1</v>
+      </c>
+      <c r="H286" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1</v>
+      </c>
+      <c r="H290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="n">
+        <v>1</v>
+      </c>
+      <c r="H292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1</v>
+      </c>
+      <c r="H293" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1</v>
+      </c>
+      <c r="H294" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1</v>
+      </c>
+      <c r="H295" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1</v>
+      </c>
+      <c r="H297" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>1</v>
+      </c>
+      <c r="H298" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>1</v>
+      </c>
+      <c r="H299" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="n">
+        <v>1</v>
+      </c>
+      <c r="H300" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" t="n">
+        <v>1</v>
+      </c>
+      <c r="H301" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>1</v>
+      </c>
+      <c r="H303" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>1</v>
+      </c>
+      <c r="H304" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
